--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/SysInstRegBankCode001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/SysInstRegBankCode001.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2720" windowWidth="13680" windowHeight="5270"/>
+    <workbookView xWindow="0" yWindow="2715" windowWidth="13680" windowHeight="5265"/>
   </bookViews>
   <sheets>
     <sheet name="机构登记银行代码" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>机构代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -34,10 +34,6 @@
   </si>
   <si>
     <t>是否理财子公司  1 是， 2 否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>社会信用代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -163,7 +159,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -205,7 +201,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -240,7 +236,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -449,17 +445,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="16.26953125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.6328125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="17.26953125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="16.25" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="17.25" style="5" customWidth="1"/>
     <col min="4" max="4" width="17" style="5" customWidth="1"/>
-    <col min="5" max="5" width="16.90625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -471,9 +466,6 @@
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -491,549 +483,549 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A179"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="31.90625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="31.875" style="3" customWidth="1"/>
     <col min="2" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" s="4"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="4"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="4"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="4"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="4"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A10" s="4"/>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A11" s="4"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A13" s="4"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A14" s="4"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A15" s="4"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A18"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A19"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A20"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A21"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A22"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A23"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A24"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A25"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A26"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A30"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A34"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A35"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A36"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A37"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A38"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A39"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A40"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A42"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A43"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A45"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A46"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A47"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A48"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A49"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A50"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A51"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A52"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A53"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A54"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A57"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A58"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A59"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A60"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A61"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A63"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A64"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A65"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A66"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A67"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A68"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A69"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A70"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A71"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A72"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A73"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A74"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A75"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A76"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A77"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A81"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A82"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A83"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A84"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A85"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A86"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A87"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A89"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A90"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A91"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A92"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A93"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A94"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A95"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A96"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A97"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A99"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A100"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A101"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A102"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A103"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A105"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A106"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A107"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A109"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A110"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A111"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A112"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A115"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A116"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A117"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A118"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A119"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A120"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A121"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A122"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A124"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A125"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A127"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A128"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A129"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A132"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A133"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A134"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A135"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A136"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A138"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A139"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A140"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A141"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A142"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A143"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A144"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A145"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A146"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A147"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A148"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A149"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A150"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A151"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A152"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A153"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A154"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A155"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A156"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A157"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A158"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A160"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A161"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A162"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A163"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A164"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A165"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A166"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A167"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A168"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A169"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A170"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A171"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A172"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A173"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A174"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A175"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A176"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A177"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A178"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A179"/>
     </row>
   </sheetData>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/SysInstRegBankCode001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/SysInstRegBankCode001.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2715" windowWidth="13680" windowHeight="5265"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>机构代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -34,6 +34,14 @@
   </si>
   <si>
     <t>是否理财子公司  1 是， 2 否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>机构代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>社会信用代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -159,7 +167,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -201,7 +209,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -236,7 +244,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -445,33 +453,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="16.25" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="17.25" style="5" customWidth="1"/>
-    <col min="4" max="4" width="17" style="5" customWidth="1"/>
+    <col min="1" max="2" width="16.25" style="5" customWidth="1"/>
+    <col min="3" max="3" width="27.625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="17.25" style="5" customWidth="1"/>
+    <col min="5" max="5" width="17" style="5" customWidth="1"/>
+    <col min="6" max="6" width="14.125" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
       <formula1>"1,2"</formula1>
     </dataValidation>
   </dataValidations>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/SysInstRegBankCode001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/SysInstRegBankCode001.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2715" windowWidth="13680" windowHeight="5265"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>机构代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -34,6 +34,10 @@
   </si>
   <si>
     <t>是否理财子公司  1 是， 2 否</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>社会信用代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -159,7 +163,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -201,7 +205,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -236,7 +240,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -445,16 +449,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="16.25" style="5" customWidth="1"/>
     <col min="2" max="2" width="27.625" style="5" customWidth="1"/>
     <col min="3" max="3" width="17.25" style="5" customWidth="1"/>
-    <col min="4" max="4" width="17" style="5" customWidth="1"/>
+    <col min="4" max="4" width="17.625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="17.25" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -466,6 +471,9 @@
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/SysInstRegBankCode001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/SysInstRegBankCode001.xlsx
@@ -4,18 +4,18 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2715" windowWidth="13680" windowHeight="5265"/>
+    <workbookView xWindow="0" yWindow="2720" windowWidth="13680" windowHeight="5270"/>
   </bookViews>
   <sheets>
     <sheet name="机构登记银行代码" sheetId="1" r:id="rId1"/>
     <sheet name="填写说明" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="152511" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>机构代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,13 +39,132 @@
   <si>
     <t>社会信用代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所属银保监局</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>银保监会</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>01 银保监会</t>
+  </si>
+  <si>
+    <t>02 北京银保监局</t>
+  </si>
+  <si>
+    <t>03 上海银保监局</t>
+  </si>
+  <si>
+    <t>04 贵州银保监局</t>
+  </si>
+  <si>
+    <t>05 宁夏银保监局</t>
+  </si>
+  <si>
+    <t>06 湖南银保监局</t>
+  </si>
+  <si>
+    <t>07 云南银保监局</t>
+  </si>
+  <si>
+    <t>08 福建银保监局</t>
+  </si>
+  <si>
+    <t>09 吉林银保监局</t>
+  </si>
+  <si>
+    <t>10 江苏银保监局</t>
+  </si>
+  <si>
+    <t>11 广东银保监局</t>
+  </si>
+  <si>
+    <t>12 青海银保监局</t>
+  </si>
+  <si>
+    <t>13 辽宁银保监局</t>
+  </si>
+  <si>
+    <t>14 湖北银保监局</t>
+  </si>
+  <si>
+    <t>15 海南银保监局</t>
+  </si>
+  <si>
+    <t>16 深圳银保监局</t>
+  </si>
+  <si>
+    <t>17 河南银保监局</t>
+  </si>
+  <si>
+    <t>18 甘肃银保监局</t>
+  </si>
+  <si>
+    <t>19 天津银保监局</t>
+  </si>
+  <si>
+    <t>20 山东银保监局</t>
+  </si>
+  <si>
+    <t>21 大连银保监局</t>
+  </si>
+  <si>
+    <t>22 宁波银保监局</t>
+  </si>
+  <si>
+    <t>23 广西银保监局</t>
+  </si>
+  <si>
+    <t>24 河北银保监局</t>
+  </si>
+  <si>
+    <t>25 西藏银保监局</t>
+  </si>
+  <si>
+    <t>26 浙江银保监局</t>
+  </si>
+  <si>
+    <t>27 四川银保监局</t>
+  </si>
+  <si>
+    <t>28 山西银保监局</t>
+  </si>
+  <si>
+    <t>29 安徽银保监局</t>
+  </si>
+  <si>
+    <t>30 重庆银保监局</t>
+  </si>
+  <si>
+    <t>31 黑龙江银保监局</t>
+  </si>
+  <si>
+    <t>32 陕西银保监局</t>
+  </si>
+  <si>
+    <t>33 江西银保监局</t>
+  </si>
+  <si>
+    <t>34 新疆银保监局</t>
+  </si>
+  <si>
+    <t>35 内蒙古银保监局</t>
+  </si>
+  <si>
+    <t>36 厦门银保监局</t>
+  </si>
+  <si>
+    <t>37 青岛银保监局</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -80,6 +199,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF373737"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -449,17 +574,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.25" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="17.25" style="5" customWidth="1"/>
-    <col min="4" max="4" width="17.625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="17.25" style="5" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="27.6328125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="17.26953125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="17.6328125" style="5" customWidth="1"/>
+    <col min="5" max="6" width="17.26953125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -474,6 +599,14 @@
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F2" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -485,555 +618,643 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>填写说明!$A$4:$A$40</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:F1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A179"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="31.90625" style="3" customWidth="1"/>
     <col min="2" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A3" s="4"/>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A4" s="4"/>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A5" s="4"/>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A6" s="4"/>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A7" s="4"/>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A8" s="4"/>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A9" s="4"/>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A10" s="4"/>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A11" s="4"/>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A12" s="4"/>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A13" s="4"/>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A14" s="4"/>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A15" s="4"/>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A16" s="4"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A17"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A18"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A19"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A20"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A21"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A22"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A23"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A24"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A25"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A26"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A27"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A28"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A29"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A30"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A31"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A32"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A33"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A34"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A35"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A36"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A37"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A38"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A39"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A40"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179"/>
     </row>
   </sheetData>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/SysInstRegBankCode001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/SysInstRegBankCode001.xlsx
@@ -15,20 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>机构代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>登记银行代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>总行机构代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>是否理财子公司</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -158,6 +150,14 @@
   </si>
   <si>
     <t>37 青岛银保监局</t>
+  </si>
+  <si>
+    <t>中债登记机构代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人行登记机构代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -219,7 +219,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00CCFF"/>
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -254,15 +254,15 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -574,46 +574,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.26953125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="27.6328125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="17.26953125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="17.6328125" style="5" customWidth="1"/>
-    <col min="5" max="6" width="17.26953125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="27.6328125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="25" style="4" customWidth="1"/>
+    <col min="4" max="4" width="17.6328125" style="4" customWidth="1"/>
+    <col min="5" max="6" width="17.26953125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F2" s="5" t="s">
-        <v>9</v>
+      <c r="F1" s="5" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
-      <formula1>"1,2"</formula1>
+      <formula1>"1 是,2 否"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -638,206 +633,206 @@
   <dimension ref="A1:A179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.90625" style="3" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="31.90625" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>4</v>
+      <c r="A1" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
+      <c r="A2" s="3"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
